--- a/data/trans_camb/P32-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P32-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,55</t>
+          <t>3,02; 8,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 4,4</t>
+          <t>0,22; 4,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,11</t>
+          <t>-0,52; 3,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,43</t>
+          <t>0,53; 4,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,72</t>
+          <t>0,91; 5,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,1</t>
+          <t>0,42; 3,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,66</t>
+          <t>2,64; 6,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,17</t>
+          <t>0,99; 4,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,89</t>
+          <t>-0,01; 2,56</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>100,61; 2769,91</t>
+          <t>84,64; 1871,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 1284,26</t>
+          <t>-20,44; 1113,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-45,93; 727,18</t>
+          <t>-52,1; 850,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>147,41; 2652,15</t>
+          <t>123,08; 2383,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,51; 1510,83</t>
+          <t>23,47; 1448,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 1025,6</t>
+          <t>-18,31; 846,85</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 4,71</t>
+          <t>-0,18; 4,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,29</t>
+          <t>0,29; 5,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,23</t>
+          <t>0,48; 6,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,3</t>
+          <t>-0,85; 3,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,62</t>
+          <t>-0,31; 3,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,38</t>
+          <t>1,67; 8,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,67</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,18</t>
+          <t>0,51; 4,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,16</t>
+          <t>1,31; 6,03</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 257,72</t>
+          <t>-7,8; 260,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,81; 273,85</t>
+          <t>3,41; 262,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 356,48</t>
+          <t>4,84; 323,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,47; —</t>
+          <t>-59,23; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,87; —</t>
+          <t>12,76; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 235,02</t>
+          <t>-1,92; 240,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,39; 281,39</t>
+          <t>9,29; 277,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41,47; 408,04</t>
+          <t>41,54; 405,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 7,33</t>
+          <t>0,35; 7,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 3,74</t>
+          <t>-2,78; 3,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 5,78</t>
+          <t>-1,71; 6,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,03</t>
+          <t>-2,69; 2,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,39</t>
+          <t>-2,17; 3,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 4,52</t>
+          <t>-3,67; 4,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 5,21</t>
+          <t>-0,12; 5,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 2,58</t>
+          <t>-2,36; 2,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 3,44</t>
+          <t>-3,28; 3,56</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 274,05</t>
+          <t>1,49; 260,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-46,16; 141,18</t>
+          <t>-47,76; 112,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,54; 213,19</t>
+          <t>-34,07; 207,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-87,88; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-91,01; —</t>
+          <t>-87,33; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 207,95</t>
+          <t>-6,41; 232,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-40,89; 118,5</t>
+          <t>-47,66; 108,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,49; 130,58</t>
+          <t>-62,16; 134,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,38</t>
+          <t>1,74; 7,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 6,24</t>
+          <t>1,09; 6,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,33; 10,16</t>
+          <t>3,49; 10,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 2,58</t>
+          <t>-3,03; 2,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 4,86</t>
+          <t>-1,32; 5,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 0,18</t>
+          <t>-4,79; 0,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,82</t>
+          <t>0,56; 4,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,93</t>
+          <t>0,93; 4,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,73</t>
+          <t>1,3; 6,15</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>41,37; 356,94</t>
+          <t>32,25; 345,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,62; 299,81</t>
+          <t>18,24; 322,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69,28; 506,71</t>
+          <t>83,27; 558,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-66,83; 158,94</t>
+          <t>-68,73; 234,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,32; 320,13</t>
+          <t>-31,94; 385,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,94; 29,21</t>
+          <t>-89,42; 29,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,65; 215,47</t>
+          <t>13,3; 208,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>23,76; 238,34</t>
+          <t>22,68; 227,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28,27; 257,77</t>
+          <t>28,87; 280,23</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,46</t>
+          <t>2,65; 5,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,94</t>
+          <t>1,17; 3,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,06</t>
+          <t>1,94; 5,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,99</t>
+          <t>-0,66; 1,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,09</t>
+          <t>0,42; 3,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,34</t>
+          <t>-0,83; 2,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,99</t>
+          <t>1,78; 3,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,31</t>
+          <t>1,26; 3,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,5</t>
+          <t>1,02; 3,55</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>77,48; 238,34</t>
+          <t>77,3; 239,37</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>38,6; 171,03</t>
+          <t>32,65; 166,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>57,58; 217,73</t>
+          <t>60,16; 230,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 213,3</t>
+          <t>-36,52; 204,3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>17,55; 339,74</t>
+          <t>16,78; 379,73</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-34,06; 222,15</t>
+          <t>-34,57; 268,77</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,46; 205,15</t>
+          <t>61,39; 195,12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>41,18; 165,44</t>
+          <t>43,92; 168,79</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>38,68; 173,03</t>
+          <t>34,37; 173,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P32-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,22</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 8,13</t>
+          <t>3,08; 8,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 4,46</t>
+          <t>0,42; 4,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,04</t>
+          <t>-0,63; 2,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,97</t>
+          <t>0,53; 4,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,71</t>
+          <t>0,9; 5,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,8</t>
+          <t>0,5; 3,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,42</t>
+          <t>2,57; 6,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,03</t>
+          <t>1,05; 3,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,56</t>
+          <t>-0,02; 2,67</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>118,34%</t>
+          <t>107,98%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>178,55%</t>
+          <t>164,27%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,64; 1871,86</t>
+          <t>113,9; 2796,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 1113,5</t>
+          <t>-0,28; 1429,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-52,1; 850,2</t>
+          <t>-49,32; 888,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>123,08; 2383,5</t>
+          <t>133,2; 2808,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,47; 1448,64</t>
+          <t>38,19; 1277,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,31; 846,85</t>
+          <t>-31,02; 1043,87</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,89</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,18</t>
+          <t>4,38</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>3,46</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,71</t>
+          <t>-0,12; 4,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 5,29</t>
+          <t>0,22; 5,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,55</t>
+          <t>0,43; 6,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,38</t>
+          <t>-0,67; 3,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,53</t>
+          <t>-0,29; 3,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 8,1</t>
+          <t>1,75; 8,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>-0,01; 3,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,07</t>
+          <t>0,49; 4,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,03</t>
+          <t>1,61; 5,92</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>101,44%</t>
+          <t>105,54%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>538,34%</t>
+          <t>563,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>153,09%</t>
+          <t>159,18%</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 260,91</t>
+          <t>-6,48; 234,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 262,33</t>
+          <t>4,02; 272,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 323,26</t>
+          <t>2,45; 326,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,23; —</t>
+          <t>-67,33; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,76; —</t>
+          <t>20,22; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 240,84</t>
+          <t>-4,03; 237,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,29; 277,77</t>
+          <t>14,19; 261,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41,54; 405,13</t>
+          <t>51,43; 395,24</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>3,31</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>4,11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>3,38</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 7,52</t>
+          <t>0,58; 7,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 3,4</t>
+          <t>-2,73; 3,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 6,04</t>
+          <t>-0,36; 7,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,84</t>
+          <t>-2,58; 2,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 3,62</t>
+          <t>-1,93; 3,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 4,6</t>
+          <t>0,59; 9,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 5,32</t>
+          <t>0,23; 5,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,56</t>
+          <t>-2,02; 2,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 3,56</t>
+          <t>0,57; 6,54</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>279,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 260,14</t>
+          <t>7,22; 266,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 112,58</t>
+          <t>-47,48; 129,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,07; 207,92</t>
+          <t>-11,83; 249,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,95; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,33; —</t>
+          <t>-23,88; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 232,64</t>
+          <t>-3,63; 220,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,66; 108,09</t>
+          <t>-43,25; 119,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,16; 134,21</t>
+          <t>10,68; 275,84</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,52</t>
+          <t>6,56</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>-1,1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,24</t>
+          <t>3,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 7,6</t>
+          <t>1,91; 7,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 6,6</t>
+          <t>1,19; 6,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,49; 10,73</t>
+          <t>3,21; 10,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 2,95</t>
+          <t>-3,05; 2,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 5,0</t>
+          <t>-1,12; 4,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 0,13</t>
+          <t>-4,04; 1,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,65</t>
+          <t>0,57; 4,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,89</t>
+          <t>0,95; 4,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,15</t>
+          <t>1,37; 5,86</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>217,44%</t>
+          <t>218,8%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-59,06%</t>
+          <t>-36,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>108,07%</t>
+          <t>116,79%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>32,25; 345,32</t>
+          <t>40,22; 375,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,24; 322,45</t>
+          <t>24,51; 323,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83,27; 558,44</t>
+          <t>63,57; 481,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-68,73; 234,18</t>
+          <t>-69,73; 179,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,94; 385,09</t>
+          <t>-33,33; 314,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-89,42; 29,6</t>
+          <t>-84,6; 139,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,3; 208,89</t>
+          <t>10,77; 213,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,68; 227,3</t>
+          <t>23,89; 223,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28,87; 280,23</t>
+          <t>28,43; 253,11</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>3,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,41</t>
+          <t>2,68; 5,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,75</t>
+          <t>1,32; 3,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,11</t>
+          <t>2,27; 5,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,92</t>
+          <t>-0,57; 2,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,12</t>
+          <t>0,45; 3,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,34</t>
+          <t>0,56; 3,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,88</t>
+          <t>1,86; 3,93</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,22</t>
+          <t>1,3; 3,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,55</t>
+          <t>2,09; 4,3</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126,06%</t>
+          <t>137,34%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>133,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>101,1%</t>
+          <t>132,81%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>77,3; 239,37</t>
+          <t>84,0; 248,52</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>32,65; 166,84</t>
+          <t>39,89; 173,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>60,16; 230,78</t>
+          <t>66,94; 250,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-36,52; 204,3</t>
+          <t>-29,65; 231,32</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>16,78; 379,73</t>
+          <t>16,4; 353,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-34,57; 268,77</t>
+          <t>22,06; 376,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,39; 195,12</t>
+          <t>65,59; 203,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>43,92; 168,79</t>
+          <t>45,83; 165,47</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>34,37; 173,14</t>
+          <t>75,12; 224,5</t>
         </is>
       </c>
     </row>
